--- a/ADEMINCOL-Central/backend/app/templates_xlsx/ESPESORES.xlsx
+++ b/ADEMINCOL-Central/backend/app/templates_xlsx/ESPESORES.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="FORMATOS_SCAN_C" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FORMATO" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2052,7 +2052,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2094,7 +2094,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2173,7 +2173,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2238,7 +2238,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
